--- a/NatioID_Government_Contacts_Top10.xlsx
+++ b/NatioID_Government_Contacts_Top10.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\ID\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E264D1A4-8052-44C1-8C38-B43E5B63ECAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -169,8 +175,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +252,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -292,7 +306,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -324,9 +338,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -358,6 +390,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -533,11 +583,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="53.28515625" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="39.42578125" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,14 +611,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -571,14 +628,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -588,14 +645,14 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -605,14 +662,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -622,14 +679,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -639,14 +696,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -656,14 +713,14 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -673,14 +730,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -690,14 +747,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -707,7 +764,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -726,16 +783,25 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-    <hyperlink ref="D4" r:id="rId3"/>
-    <hyperlink ref="D5" r:id="rId4"/>
-    <hyperlink ref="D6" r:id="rId5"/>
-    <hyperlink ref="D7" r:id="rId6"/>
-    <hyperlink ref="D8" r:id="rId7"/>
-    <hyperlink ref="D9" r:id="rId8"/>
-    <hyperlink ref="D10" r:id="rId9"/>
-    <hyperlink ref="D11" r:id="rId10"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C2" r:id="rId11" xr:uid="{20832A39-FCD0-45AA-968C-8D3F198B096A}"/>
+    <hyperlink ref="C3" r:id="rId12" xr:uid="{7CB4A0C0-43A6-417F-8EFD-690CA8BD475A}"/>
+    <hyperlink ref="C4" r:id="rId13" xr:uid="{4CD4C69E-FE34-4CF9-B1B6-00CE30749C66}"/>
+    <hyperlink ref="C5" r:id="rId14" xr:uid="{7222FCD0-9514-423D-8582-999913031FF7}"/>
+    <hyperlink ref="C6" r:id="rId15" xr:uid="{454C9A0F-84F7-4F0A-AA28-931695B277E2}"/>
+    <hyperlink ref="C10" r:id="rId16" xr:uid="{97E1F88A-7421-4AC9-B2E4-BB1C32C08297}"/>
+    <hyperlink ref="C9" r:id="rId17" xr:uid="{9AFECDDE-0088-4F1E-B31F-58DAF8B4E744}"/>
+    <hyperlink ref="C7" r:id="rId18" xr:uid="{93ED939B-26CA-4457-A41D-8511F148DCA1}"/>
+    <hyperlink ref="C8" r:id="rId19" xr:uid="{667CC8E8-09FE-4EEA-8666-9B7E29082888}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
